--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -171,7 +171,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -208,7 +210,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -12563,7 +12565,7 @@
         <v>4.66666666666667</v>
       </c>
       <c r="K15" t="n">
-        <v>0.307692307692308</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="16">
@@ -12586,7 +12588,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>0.153846153846154</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="17">
@@ -12606,10 +12608,10 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.33333333333333</v>
+        <v>3.66666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.0666666666666666</v>
       </c>
     </row>
     <row r="18">
@@ -12629,10 +12631,10 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>4.33333333333333</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>0.230769230769231</v>
+        <v>0.133333333333333</v>
       </c>
     </row>
     <row r="19">
@@ -12652,10 +12654,10 @@
         <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>3.33333333333333</v>
+        <v>4.33333333333333</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="20">
@@ -12678,7 +12680,7 @@
         <v>6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.615384615384615</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="21">
@@ -12698,10 +12700,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>7.33333333333333</v>
+        <v>8</v>
       </c>
       <c r="K21" t="n">
-        <v>0.923076923076923</v>
+        <v>0.933333333333333</v>
       </c>
     </row>
     <row r="22">
@@ -12721,7 +12723,7 @@
         <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>7.66666666666667</v>
+        <v>8.33333333333333</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -12744,10 +12746,10 @@
         <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>5.66666666666667</v>
+        <v>6</v>
       </c>
       <c r="K23" t="n">
-        <v>0.538461538461538</v>
+        <v>0.533333333333333</v>
       </c>
     </row>
     <row r="24">
@@ -12770,7 +12772,7 @@
         <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.846153846153846</v>
+        <v>0.733333333333333</v>
       </c>
     </row>
     <row r="25">
@@ -12793,7 +12795,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.384615384615385</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="26">
@@ -12839,7 +12841,7 @@
         <v>4.66666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>0.307692307692308</v>
+        <v>0.266666666666667</v>
       </c>
     </row>
     <row r="28">
@@ -65607,10 +65609,10 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>39941.6666666667</v>
+        <v>39966.3333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>0.970812231065078</v>
+        <v>0.742493986279809</v>
       </c>
     </row>
     <row r="16">
@@ -65630,10 +65632,10 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>34516.6666666667</v>
+        <v>34548.6666666667</v>
       </c>
       <c r="K16" t="n">
-        <v>0.660942081413503</v>
+        <v>0.501158197962759</v>
       </c>
     </row>
     <row r="17">
@@ -65653,10 +65655,10 @@
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>33813.6666666667</v>
+        <v>33861.3333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>0.620787479532386</v>
+        <v>0.470540195408785</v>
       </c>
     </row>
     <row r="18">
@@ -65676,10 +65678,10 @@
         <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>26954.6666666667</v>
+        <v>27006</v>
       </c>
       <c r="K18" t="n">
-        <v>0.229008796313926</v>
+        <v>0.165161999227868</v>
       </c>
     </row>
     <row r="19">
@@ -65699,10 +65701,10 @@
         <v>5</v>
       </c>
       <c r="J19" t="n">
-        <v>24099</v>
+        <v>24173.6666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0658961958798219</v>
+        <v>0.038992664746236</v>
       </c>
     </row>
     <row r="20">
@@ -65722,10 +65724,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="n">
-        <v>25882.6666666667</v>
+        <v>26036.3333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>0.167777312364343</v>
+        <v>0.121967154693671</v>
       </c>
     </row>
     <row r="21">
@@ -65745,10 +65747,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>28755</v>
+        <v>29297.3333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>0.331841894825026</v>
+        <v>0.267231906869005</v>
       </c>
     </row>
     <row r="22">
@@ -65768,10 +65770,10 @@
         <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>33684</v>
+        <v>35595</v>
       </c>
       <c r="K22" t="n">
-        <v>0.613381059365599</v>
+        <v>0.547768241617913</v>
       </c>
     </row>
     <row r="23">
@@ -65791,7 +65793,7 @@
         <v>9</v>
       </c>
       <c r="J23" t="n">
-        <v>40452.6666666667</v>
+        <v>45747</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
@@ -65814,10 +65816,10 @@
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>38830</v>
+        <v>43787.3333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>0.907315029892236</v>
+        <v>0.912704540729962</v>
       </c>
     </row>
     <row r="25">
@@ -65837,10 +65839,10 @@
         <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>33225</v>
+        <v>35691.3333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>0.587163474353604</v>
+        <v>0.552059513556856</v>
       </c>
     </row>
     <row r="26">
@@ -65860,7 +65862,7 @@
         <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>22945.3333333333</v>
+        <v>23298.3333333333</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -65883,10 +65885,10 @@
         <v>13</v>
       </c>
       <c r="J27" t="n">
-        <v>39941.6666666667</v>
+        <v>39966.3333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.970812231065078</v>
+        <v>0.742493986279809</v>
       </c>
     </row>
     <row r="28">

--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Shortname</t>
   </si>
@@ -113,49 +113,25 @@
     <t xml:space="preserve">Rebound_Intensity</t>
   </si>
   <si>
-    <t xml:space="preserve">Date_Start_Deficit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date_Trough</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date_Recovery</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date_Balance</t>
+    <t xml:space="preserve">Relative_Deficit_percent</t>
   </si>
   <si>
     <t xml:space="preserve">Suppression_Months</t>
   </si>
   <si>
-    <t xml:space="preserve">Payback_Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Debt Repaid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recovered</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deficit_Magnitude</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log_Rebound</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster</t>
   </si>
   <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
   </si>
 </sst>
 </file>
@@ -163,18 +139,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -197,9 +168,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -778,6 +748,9 @@
       <c r="D1" t="s">
         <v>31</v>
       </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
@@ -792,6 +765,9 @@
       <c r="D2" t="n">
         <v>2.26864092765106</v>
       </c>
+      <c r="E2" t="n">
+        <v>27.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -806,6 +782,9 @@
       <c r="D3" t="n">
         <v>4.06120153402493</v>
       </c>
+      <c r="E3" t="n">
+        <v>82.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -820,6 +799,9 @@
       <c r="D4" t="n">
         <v>0.656981044371095</v>
       </c>
+      <c r="E4" t="n">
+        <v>52.73</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -834,6 +816,9 @@
       <c r="D5" t="n">
         <v>3.6807482079489</v>
       </c>
+      <c r="E5" t="n">
+        <v>53.3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -848,6 +833,9 @@
       <c r="D6" t="n">
         <v>7.96248900453676</v>
       </c>
+      <c r="E6" t="n">
+        <v>75.3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -862,6 +850,9 @@
       <c r="D7" t="n">
         <v>0.0683963575558215</v>
       </c>
+      <c r="E7" t="n">
+        <v>82.67</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -876,6 +867,9 @@
       <c r="D8" t="n">
         <v>4.01123798425685</v>
       </c>
+      <c r="E8" t="n">
+        <v>52.08</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -890,6 +884,9 @@
       <c r="D9" t="n">
         <v>6.85014917582655</v>
       </c>
+      <c r="E9" t="n">
+        <v>16.21</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -904,6 +901,9 @@
       <c r="D10" t="n">
         <v>5.25376762935413</v>
       </c>
+      <c r="E10" t="n">
+        <v>26.83</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -918,6 +918,9 @@
       <c r="D11" t="n">
         <v>2.10577811305707</v>
       </c>
+      <c r="E11" t="n">
+        <v>15.86</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -932,6 +935,9 @@
       <c r="D12" t="n">
         <v>4.21262045164963</v>
       </c>
+      <c r="E12" t="n">
+        <v>18.22</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -946,6 +952,9 @@
       <c r="D13" t="n">
         <v>5.92905752727299</v>
       </c>
+      <c r="E13" t="n">
+        <v>49.04</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -960,6 +969,9 @@
       <c r="D14" t="n">
         <v>4.03899779835412</v>
       </c>
+      <c r="E14" t="n">
+        <v>8.41</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -974,6 +986,9 @@
       <c r="D15" t="n">
         <v>2.85154236856698</v>
       </c>
+      <c r="E15" t="n">
+        <v>19.35</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -988,6 +1003,9 @@
       <c r="D16" t="n">
         <v>2.60435297119371</v>
       </c>
+      <c r="E16" t="n">
+        <v>48.14</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -1002,6 +1020,9 @@
       <c r="D17" t="n">
         <v>2.49338008207189</v>
       </c>
+      <c r="E17" t="n">
+        <v>35.26</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -1016,6 +1037,9 @@
       <c r="D18" t="n">
         <v>1.82697939334667</v>
       </c>
+      <c r="E18" t="n">
+        <v>34.31</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -1030,6 +1054,9 @@
       <c r="D19" t="n">
         <v>0.987770430596723</v>
       </c>
+      <c r="E19" t="n">
+        <v>24.65</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -1044,6 +1071,9 @@
       <c r="D20" t="n">
         <v>3.06490315259725</v>
       </c>
+      <c r="E20" t="n">
+        <v>20.92</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -1058,6 +1088,9 @@
       <c r="D21" t="n">
         <v>2.84453657101213</v>
       </c>
+      <c r="E21" t="n">
+        <v>23.24</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1072,6 +1105,9 @@
       <c r="D22" t="n">
         <v>3.2674244746727</v>
       </c>
+      <c r="E22" t="n">
+        <v>24.49</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -1086,6 +1122,9 @@
       <c r="D23" t="n">
         <v>1.55568983384528</v>
       </c>
+      <c r="E23" t="n">
+        <v>24.16</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -1099,6 +1138,9 @@
       </c>
       <c r="D24" t="n">
         <v>16.2242913160414</v>
+      </c>
+      <c r="E24" t="n">
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>
@@ -1117,769 +1159,356 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
         <v>2</v>
-      </c>
-      <c r="G1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-      <c r="I1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K1" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>45689</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
+        <v>31</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.26864092765106</v>
+      </c>
+      <c r="E2" t="n">
         <v>213705.771933232</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.279365719412144</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2.26864092765106</v>
-      </c>
-      <c r="I2" t="n">
-        <v>31</v>
-      </c>
-      <c r="J2" t="n">
-        <v>28</v>
-      </c>
-      <c r="K2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45139</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" t="n">
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="n">
+        <v>41</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.06120153402493</v>
+      </c>
+      <c r="E3" t="n">
         <v>1463430.69537175</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.825178955136324</v>
-      </c>
-      <c r="H3" t="n">
-        <v>4.06120153402493</v>
-      </c>
-      <c r="I3" t="n">
-        <v>41</v>
-      </c>
-      <c r="J3"/>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C4" s="1" t="n">
-        <v>45505</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>45536</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" t="n">
+      <c r="B4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="n">
+        <v>58</v>
+      </c>
+      <c r="D4" t="n">
+        <v>3.6807482079489</v>
+      </c>
+      <c r="E4" t="n">
         <v>3745.37810794006</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.532969487397903</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.6807482079489</v>
-      </c>
-      <c r="I4" t="n">
-        <v>56</v>
-      </c>
-      <c r="J4"/>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>45658</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>45689</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" t="n">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>61</v>
+      </c>
+      <c r="D5" t="n">
+        <v>7.96248900453676</v>
+      </c>
+      <c r="E5" t="n">
         <v>8693.5799836956</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.752979061768441</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7.96248900453676</v>
-      </c>
-      <c r="I5" t="n">
-        <v>61</v>
-      </c>
-      <c r="J5"/>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="C6" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" t="n">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="n">
+        <v>34</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.01123798425685</v>
+      </c>
+      <c r="E6" t="n">
         <v>136125.791770204</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.520828806653862</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.01123798425685</v>
-      </c>
-      <c r="I6" t="n">
-        <v>34</v>
-      </c>
-      <c r="J6"/>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L6" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>43983</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>44621</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="n">
+        <v>22</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6.85014917582655</v>
+      </c>
+      <c r="E7" t="n">
         <v>1649.43203417845</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.162131326836121</v>
-      </c>
-      <c r="H7" t="n">
-        <v>6.85014917582655</v>
-      </c>
-      <c r="I7" t="n">
-        <v>22</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6</v>
-      </c>
-      <c r="K7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="B8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="n">
+        <v>26</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.25376762935413</v>
+      </c>
+      <c r="E8" t="n">
         <v>1179.28089114645</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.268306149334371</v>
-      </c>
-      <c r="H8" t="n">
-        <v>5.25376762935413</v>
-      </c>
-      <c r="I8" t="n">
-        <v>25</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6</v>
-      </c>
-      <c r="K8" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>43922</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44044</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>45078</v>
-      </c>
-      <c r="F9" t="n">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="n">
+        <v>25</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.10577811305707</v>
+      </c>
+      <c r="E9" t="n">
         <v>1096.79125120878</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.158615236724181</v>
-      </c>
-      <c r="H9" t="n">
-        <v>2.10577811305707</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>14</v>
-      </c>
-      <c r="K9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>43952</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>44013</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.21262045164963</v>
+      </c>
+      <c r="E10" t="n">
         <v>26.0660434837536</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.182195878553904</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.21262045164963</v>
-      </c>
-      <c r="I10" t="n">
-        <v>3</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="s">
-        <v>39</v>
-      </c>
-      <c r="L10" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>44105</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>44805</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.92905752727299</v>
+      </c>
+      <c r="E11" t="n">
         <v>56282.6746473634</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.490358290163932</v>
-      </c>
-      <c r="H11" t="n">
-        <v>5.92905752727299</v>
-      </c>
-      <c r="I11" t="n">
-        <v>9</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3</v>
-      </c>
-      <c r="K11" t="s">
-        <v>39</v>
-      </c>
-      <c r="L11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>44378</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.03899779835412</v>
+      </c>
+      <c r="E12" t="n">
         <v>276.479934279954</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0840752991672098</v>
-      </c>
-      <c r="H12" t="n">
-        <v>4.03899779835412</v>
-      </c>
-      <c r="I12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="E13" s="1"/>
-      <c r="F13" t="n">
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.85154236856698</v>
+      </c>
+      <c r="E13" t="n">
         <v>249.981486597994</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.193486895277608</v>
-      </c>
-      <c r="H13" t="n">
-        <v>2.85154236856698</v>
-      </c>
-      <c r="I13" t="n">
-        <v>27</v>
-      </c>
-      <c r="J13"/>
-      <c r="K13" t="s">
-        <v>40</v>
-      </c>
-      <c r="L13" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>44713</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>44743</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>45474</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2.60435297119371</v>
+      </c>
+      <c r="E14" t="n">
         <v>1002.62606493129</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.48142394922171</v>
-      </c>
-      <c r="H14" t="n">
-        <v>2.60435297119371</v>
-      </c>
-      <c r="I14" t="n">
-        <v>30</v>
-      </c>
-      <c r="J14" t="n">
-        <v>25</v>
-      </c>
-      <c r="K14" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>45200</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="E15" s="1"/>
-      <c r="F15" t="n">
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>46</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.49338008207189</v>
+      </c>
+      <c r="E15" t="n">
         <v>614.318530576056</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.352586808781139</v>
-      </c>
-      <c r="H15" t="n">
-        <v>2.49338008207189</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15"/>
-      <c r="K15" t="s">
-        <v>40</v>
-      </c>
-      <c r="L15" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>44835</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>45689</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="n">
+        <v>36</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.82697939334667</v>
+      </c>
+      <c r="E16" t="n">
         <v>9741.16384132806</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.343081309845054</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.82697939334667</v>
-      </c>
-      <c r="I16" t="n">
-        <v>34</v>
-      </c>
-      <c r="J16" t="n">
-        <v>28</v>
-      </c>
-      <c r="K16" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>44958</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>45413</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3.06490315259725</v>
+      </c>
+      <c r="E17" t="n">
         <v>4793.86718554297</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.209175973782021</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.06490315259725</v>
-      </c>
-      <c r="I17" t="n">
-        <v>34</v>
-      </c>
-      <c r="J17" t="n">
-        <v>15</v>
-      </c>
-      <c r="K17" t="s">
-        <v>39</v>
-      </c>
-      <c r="L17" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>45108</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>45047</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>45536</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>41</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2.84453657101213</v>
+      </c>
+      <c r="E18" t="n">
         <v>3838.25573626451</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.232350403525653</v>
-      </c>
-      <c r="H18" t="n">
-        <v>2.84453657101213</v>
-      </c>
-      <c r="I18" t="n">
-        <v>38</v>
-      </c>
-      <c r="J18" t="n">
-        <v>14</v>
-      </c>
-      <c r="K18" t="s">
-        <v>39</v>
-      </c>
-      <c r="L18" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>43862</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>45383</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="n">
+        <v>35</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.2674244746727</v>
+      </c>
+      <c r="E19" t="n">
         <v>1599.7034947874</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.244913673142701</v>
-      </c>
-      <c r="H19" t="n">
-        <v>3.2674244746727</v>
-      </c>
-      <c r="I19" t="n">
-        <v>35</v>
-      </c>
-      <c r="J19" t="n">
-        <v>16</v>
-      </c>
-      <c r="K19" t="s">
-        <v>39</v>
-      </c>
-      <c r="L19" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>43891</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>45170</v>
-      </c>
-      <c r="E20" s="1"/>
-      <c r="F20" t="n">
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" t="n">
+        <v>46</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.55568983384528</v>
+      </c>
+      <c r="E20" t="n">
         <v>1515.37339858964</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.241556384788178</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.55568983384528</v>
-      </c>
-      <c r="I20" t="n">
-        <v>42</v>
-      </c>
-      <c r="J20"/>
-      <c r="K20" t="s">
-        <v>40</v>
-      </c>
-      <c r="L20" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>43831</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>44652</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>44682</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>44866</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="n">
+        <v>28</v>
+      </c>
+      <c r="D21" t="n">
+        <v>16.2242913160414</v>
+      </c>
+      <c r="E21" t="n">
         <v>146.669525368677</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.13893507565017</v>
-      </c>
-      <c r="H21" t="n">
-        <v>16.2242913160414</v>
-      </c>
-      <c r="I21" t="n">
-        <v>28</v>
-      </c>
-      <c r="J21" t="n">
-        <v>7</v>
-      </c>
-      <c r="K21" t="s">
-        <v>39</v>
-      </c>
-      <c r="L21" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1904,15 +1533,12 @@
         <v>31</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1927,15 +1553,12 @@
         <v>2.26864092765106</v>
       </c>
       <c r="D2" t="n">
-        <v>0.279365719412144</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.106994709622438</v>
+        <v>-0.553826886638229</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
       </c>
       <c r="F2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G2" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1950,15 +1573,12 @@
         <v>4.06120153402493</v>
       </c>
       <c r="D3" t="n">
-        <v>0.825178955136324</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.261305452583169</v>
+        <v>-0.0834518565407574</v>
+      </c>
+      <c r="E3" t="s">
+        <v>37</v>
       </c>
       <c r="F3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G3" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1973,15 +1593,12 @@
         <v>0.656981044371095</v>
       </c>
       <c r="D4" t="n">
-        <v>0.52732133779276</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.183930419209969</v>
+        <v>-0.277924654805158</v>
+      </c>
+      <c r="E4" t="s">
+        <v>36</v>
       </c>
       <c r="F4" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1996,15 +1613,12 @@
         <v>3.6807482079489</v>
       </c>
       <c r="D5" t="n">
-        <v>0.532969487397903</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.185533510636111</v>
+        <v>-0.27329765370145</v>
+      </c>
+      <c r="E5" t="s">
+        <v>37</v>
       </c>
       <c r="F5" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2019,15 +1633,12 @@
         <v>7.96248900453676</v>
       </c>
       <c r="D6" t="n">
-        <v>0.752979061768441</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.243776728750535</v>
+        <v>-0.12321710014041</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
       </c>
       <c r="F6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2042,15 +1653,12 @@
         <v>0.0683963575558215</v>
       </c>
       <c r="D7" t="n">
-        <v>0.826678417215016</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.261662097477422</v>
+        <v>-0.0826634007135609</v>
+      </c>
+      <c r="E7" t="s">
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2065,15 +1673,12 @@
         <v>4.01123798425685</v>
       </c>
       <c r="D8" t="n">
-        <v>0.520828806653862</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.182080330088535</v>
+        <v>-0.28330500327083</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2088,15 +1693,12 @@
         <v>6.85014917582655</v>
       </c>
       <c r="D9" t="n">
-        <v>0.162131326836121</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0652552083447888</v>
+        <v>-0.790133063142851</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2111,15 +1713,12 @@
         <v>5.25376762935413</v>
       </c>
       <c r="D10" t="n">
-        <v>0.268306149334371</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.10322409811839</v>
+        <v>-0.571369373577109</v>
+      </c>
+      <c r="E10" t="s">
+        <v>38</v>
       </c>
       <c r="F10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G10" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2134,15 +1733,12 @@
         <v>2.10577811305707</v>
       </c>
       <c r="D11" t="n">
-        <v>0.158615236724181</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0639392355230617</v>
+        <v>-0.799655096290825</v>
+      </c>
+      <c r="E11" t="s">
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2157,15 +1753,12 @@
         <v>4.21262045164963</v>
       </c>
       <c r="D12" t="n">
-        <v>0.182195878553904</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0726894409505976</v>
+        <v>-0.739461451410998</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G12" t="s">
         <v>11</v>
       </c>
     </row>
@@ -2180,15 +1773,12 @@
         <v>5.92905752727299</v>
       </c>
       <c r="D13" t="n">
-        <v>0.490358290163932</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.173290687697955</v>
+        <v>-0.30948647797175</v>
+      </c>
+      <c r="E13" t="s">
+        <v>37</v>
       </c>
       <c r="F13" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2203,15 +1793,12 @@
         <v>4.03899779835412</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0840752991672098</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0350594490631195</v>
+        <v>-1.07533157864982</v>
+      </c>
+      <c r="E14" t="s">
+        <v>38</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2226,15 +1813,12 @@
         <v>2.85154236856698</v>
       </c>
       <c r="D15" t="n">
-        <v>0.193486895277608</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0768176547295621</v>
+        <v>-0.713348444088747</v>
+      </c>
+      <c r="E15" t="s">
+        <v>38</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2249,15 +1833,12 @@
         <v>2.60435297119371</v>
       </c>
       <c r="D16" t="n">
-        <v>0.48142394922171</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.170679361329995</v>
+        <v>-0.317472308834312</v>
+      </c>
+      <c r="E16" t="s">
+        <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2272,15 +1853,12 @@
         <v>2.49338008207189</v>
       </c>
       <c r="D17" t="n">
-        <v>0.352586808781139</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.131165147615794</v>
+        <v>-0.452733939854977</v>
+      </c>
+      <c r="E17" t="s">
+        <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2295,15 +1873,12 @@
         <v>1.82697939334667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.343081309845054</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.12810230555636</v>
+        <v>-0.464602940504748</v>
+      </c>
+      <c r="E18" t="s">
+        <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2318,15 +1893,12 @@
         <v>0.987770430596723</v>
       </c>
       <c r="D19" t="n">
-        <v>0.246484884507112</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.0956870164018019</v>
+        <v>-0.608209708339822</v>
+      </c>
+      <c r="E19" t="s">
+        <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2341,15 +1913,12 @@
         <v>3.06490315259725</v>
       </c>
       <c r="D20" t="n">
-        <v>0.209175973782021</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0824895091991681</v>
+        <v>-0.679488200555833</v>
+      </c>
+      <c r="E20" t="s">
+        <v>38</v>
       </c>
       <c r="F20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2364,15 +1933,12 @@
         <v>2.84453657101213</v>
       </c>
       <c r="D21" t="n">
-        <v>0.232350403525653</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.0907342116275728</v>
+        <v>-0.633856568940172</v>
+      </c>
+      <c r="E21" t="s">
+        <v>38</v>
       </c>
       <c r="F21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2387,15 +1953,12 @@
         <v>3.2674244746727</v>
       </c>
       <c r="D22" t="n">
-        <v>0.244913673142701</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.0951392369115735</v>
+        <v>-0.610986968224968</v>
+      </c>
+      <c r="E22" t="s">
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2410,15 +1973,12 @@
         <v>1.55568983384528</v>
       </c>
       <c r="D23" t="n">
-        <v>0.241556384788178</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.0939664476491924</v>
+        <v>-0.616981478808273</v>
+      </c>
+      <c r="E23" t="s">
+        <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -128,10 +128,10 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
   </si>
 </sst>
 </file>

--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -10,12 +10,14 @@
     <sheet name="panel B" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="panel C" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="panel D" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="cluster selection" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="cluster summary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t xml:space="preserve">Shortname</t>
   </si>
@@ -23,7 +25,7 @@
     <t xml:space="preserve">Group</t>
   </si>
   <si>
-    <t xml:space="preserve">Max_Deficit_Raw</t>
+    <t xml:space="preserve">Absolute_Suppression</t>
   </si>
   <si>
     <t xml:space="preserve">Pneumonia</t>
@@ -110,16 +112,13 @@
     <t xml:space="preserve">Relative_Deficit</t>
   </si>
   <si>
+    <t xml:space="preserve">Relative_Deficit_percent</t>
+  </si>
+  <si>
     <t xml:space="preserve">Rebound_Intensity</t>
   </si>
   <si>
-    <t xml:space="preserve">Relative_Deficit_percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Suppression_Months</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log_Rebound</t>
+    <t xml:space="preserve">Recovery_Period</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster</t>
@@ -132,6 +131,27 @@
   </si>
   <si>
     <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TotalWithinSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelativeReductionPct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SelectedK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSS_K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WSS_K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reduction_K3_vs_K2_Pct</t>
   </si>
 </sst>
 </file>
@@ -479,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>213705.771933232</v>
+        <v>208566.151363084</v>
       </c>
     </row>
     <row r="3">
@@ -490,7 +510,7 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>1463430.69537175</v>
+        <v>1233435.52803022</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>174707.761078267</v>
+        <v>198994.908037956</v>
       </c>
     </row>
     <row r="5">
@@ -512,7 +532,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3745.37810794006</v>
+        <v>8436.7368576976</v>
       </c>
     </row>
     <row r="6">
@@ -523,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>8693.5799836956</v>
+        <v>8600.00859599406</v>
       </c>
     </row>
     <row r="7">
@@ -534,7 +554,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>2036.62855184469</v>
+        <v>1906.1196847482</v>
       </c>
     </row>
     <row r="8">
@@ -545,7 +565,7 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>136125.791770204</v>
+        <v>137280.410343388</v>
       </c>
     </row>
     <row r="9">
@@ -556,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1649.43203417845</v>
+        <v>4027.18165844523</v>
       </c>
     </row>
     <row r="10">
@@ -567,7 +587,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>1179.28089114645</v>
+        <v>710.483364008151</v>
       </c>
     </row>
     <row r="11">
@@ -578,7 +598,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>1096.79125120878</v>
+        <v>940.730508061435</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +609,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.0660434837536</v>
+        <v>31.4334749638212</v>
       </c>
     </row>
     <row r="13">
@@ -600,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>56282.6746473634</v>
+        <v>55530.4852673625</v>
       </c>
     </row>
     <row r="14">
@@ -611,7 +631,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>276.479934279954</v>
+        <v>521.658880940343</v>
       </c>
     </row>
     <row r="15">
@@ -622,7 +642,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>249.981486597994</v>
+        <v>705.868129697753</v>
       </c>
     </row>
     <row r="16">
@@ -633,7 +653,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1002.62606493129</v>
+        <v>1021.62267886647</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +664,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>614.318530576056</v>
+        <v>1062.12555896263</v>
       </c>
     </row>
     <row r="18">
@@ -655,7 +675,7 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>9741.16384132806</v>
+        <v>8799.23152575949</v>
       </c>
     </row>
     <row r="19">
@@ -666,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>37927.8163321939</v>
+        <v>5061.21321793091</v>
       </c>
     </row>
     <row r="20">
@@ -677,7 +697,7 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>4793.86718554297</v>
+        <v>4501.92785514261</v>
       </c>
     </row>
     <row r="21">
@@ -688,7 +708,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>3838.25573626451</v>
+        <v>4016.24392719755</v>
       </c>
     </row>
     <row r="22">
@@ -699,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>1599.7034947874</v>
+        <v>1637.46763124693</v>
       </c>
     </row>
     <row r="23">
@@ -710,7 +730,7 @@
         <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>1515.37339858964</v>
+        <v>1615.14096911446</v>
       </c>
     </row>
     <row r="24">
@@ -721,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>146.669525368677</v>
+        <v>163.934353869879</v>
       </c>
     </row>
   </sheetData>
@@ -760,13 +780,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>0.279365719412144</v>
+        <v>0.274491213557867</v>
       </c>
       <c r="D2" t="n">
-        <v>2.26864092765106</v>
+        <v>27.45</v>
       </c>
       <c r="E2" t="n">
-        <v>27.94</v>
+        <v>2.25623000075569</v>
       </c>
     </row>
     <row r="3">
@@ -777,13 +797,13 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>0.825178955136324</v>
+        <v>0.770826612703138</v>
       </c>
       <c r="D3" t="n">
-        <v>4.06120153402493</v>
+        <v>77.08</v>
       </c>
       <c r="E3" t="n">
-        <v>82.52</v>
+        <v>5.38441292750874</v>
       </c>
     </row>
     <row r="4">
@@ -794,13 +814,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.52732133779276</v>
+        <v>0.593818056246074</v>
       </c>
       <c r="D4" t="n">
-        <v>0.656981044371095</v>
+        <v>59.38</v>
       </c>
       <c r="E4" t="n">
-        <v>52.73</v>
+        <v>1.31801984955663</v>
       </c>
     </row>
     <row r="5">
@@ -811,13 +831,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.532969487397903</v>
+        <v>0.629854617326747</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6807482079489</v>
+        <v>62.99</v>
       </c>
       <c r="E5" t="n">
-        <v>53.3</v>
+        <v>1.35575123440927</v>
       </c>
     </row>
     <row r="6">
@@ -828,13 +848,13 @@
         <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>0.752979061768441</v>
+        <v>0.750960717843188</v>
       </c>
       <c r="D6" t="n">
-        <v>7.96248900453676</v>
+        <v>75.1</v>
       </c>
       <c r="E6" t="n">
-        <v>75.3</v>
+        <v>7.81258703681891</v>
       </c>
     </row>
     <row r="7">
@@ -845,13 +865,13 @@
         <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.826678417215016</v>
+        <v>0.816983242312284</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0683963575558215</v>
+        <v>81.7</v>
       </c>
       <c r="E7" t="n">
-        <v>82.67</v>
+        <v>0.0752496396590436</v>
       </c>
     </row>
     <row r="8">
@@ -862,13 +882,13 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>0.520828806653862</v>
+        <v>0.522936315833308</v>
       </c>
       <c r="D8" t="n">
-        <v>4.01123798425685</v>
+        <v>52.29</v>
       </c>
       <c r="E8" t="n">
-        <v>52.08</v>
+        <v>3.98803982999847</v>
       </c>
     </row>
     <row r="9">
@@ -879,13 +899,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>0.162131326836121</v>
+        <v>0.315803347718012</v>
       </c>
       <c r="D9" t="n">
-        <v>6.85014917582655</v>
+        <v>31.58</v>
       </c>
       <c r="E9" t="n">
-        <v>16.21</v>
+        <v>2.05501599388022</v>
       </c>
     </row>
     <row r="10">
@@ -896,13 +916,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.268306149334371</v>
+        <v>0.203899198184402</v>
       </c>
       <c r="D10" t="n">
-        <v>5.25376762935413</v>
+        <v>20.39</v>
       </c>
       <c r="E10" t="n">
-        <v>26.83</v>
+        <v>8.51681481550408</v>
       </c>
     </row>
     <row r="11">
@@ -913,13 +933,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.158615236724181</v>
+        <v>0.139187456422384</v>
       </c>
       <c r="D11" t="n">
-        <v>2.10577811305707</v>
+        <v>13.92</v>
       </c>
       <c r="E11" t="n">
-        <v>15.86</v>
+        <v>2.13890275428367</v>
       </c>
     </row>
     <row r="12">
@@ -930,13 +950,13 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.182195878553904</v>
+        <v>0.211768099961836</v>
       </c>
       <c r="D12" t="n">
-        <v>4.21262045164963</v>
+        <v>21.18</v>
       </c>
       <c r="E12" t="n">
-        <v>18.22</v>
+        <v>4.3070090372524</v>
       </c>
     </row>
     <row r="13">
@@ -947,13 +967,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.490358290163932</v>
+        <v>0.486996377527185</v>
       </c>
       <c r="D13" t="n">
-        <v>5.92905752727299</v>
+        <v>48.7</v>
       </c>
       <c r="E13" t="n">
-        <v>49.04</v>
+        <v>5.54954574978561</v>
       </c>
     </row>
     <row r="14">
@@ -964,13 +984,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0840752991672098</v>
+        <v>0.138127084649609</v>
       </c>
       <c r="D14" t="n">
-        <v>4.03899779835412</v>
+        <v>13.81</v>
       </c>
       <c r="E14" t="n">
-        <v>8.41</v>
+        <v>5.91244538148531</v>
       </c>
     </row>
     <row r="15">
@@ -981,13 +1001,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.193486895277608</v>
+        <v>0.311247431212778</v>
       </c>
       <c r="D15" t="n">
-        <v>2.85154236856698</v>
+        <v>31.12</v>
       </c>
       <c r="E15" t="n">
-        <v>19.35</v>
+        <v>14.5859570297162</v>
       </c>
     </row>
     <row r="16">
@@ -998,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.48142394922171</v>
+        <v>0.486111369628677</v>
       </c>
       <c r="D16" t="n">
-        <v>2.60435297119371</v>
+        <v>48.61</v>
       </c>
       <c r="E16" t="n">
-        <v>48.14</v>
+        <v>2.6757566376574</v>
       </c>
     </row>
     <row r="17">
@@ -1015,13 +1035,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.352586808781139</v>
+        <v>0.307583822489706</v>
       </c>
       <c r="D17" t="n">
-        <v>2.49338008207189</v>
+        <v>30.76</v>
       </c>
       <c r="E17" t="n">
-        <v>35.26</v>
+        <v>0.708060899050319</v>
       </c>
     </row>
     <row r="18">
@@ -1032,13 +1052,13 @@
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>0.343081309845054</v>
+        <v>0.320540501707639</v>
       </c>
       <c r="D18" t="n">
-        <v>1.82697939334667</v>
+        <v>32.05</v>
       </c>
       <c r="E18" t="n">
-        <v>34.31</v>
+        <v>1.89154911330883</v>
       </c>
     </row>
     <row r="19">
@@ -1049,13 +1069,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.246484884507112</v>
+        <v>0.124399328837739</v>
       </c>
       <c r="D19" t="n">
-        <v>0.987770430596723</v>
+        <v>12.44</v>
       </c>
       <c r="E19" t="n">
-        <v>24.65</v>
+        <v>1.55601404266236</v>
       </c>
     </row>
     <row r="20">
@@ -1066,13 +1086,13 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.209175973782021</v>
+        <v>0.212817585744397</v>
       </c>
       <c r="D20" t="n">
-        <v>3.06490315259725</v>
+        <v>21.28</v>
       </c>
       <c r="E20" t="n">
-        <v>20.92</v>
+        <v>3.09913502283175</v>
       </c>
     </row>
     <row r="21">
@@ -1083,13 +1103,13 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.232350403525653</v>
+        <v>0.246482374091248</v>
       </c>
       <c r="D21" t="n">
-        <v>2.84453657101213</v>
+        <v>24.65</v>
       </c>
       <c r="E21" t="n">
-        <v>23.24</v>
+        <v>2.52831076732444</v>
       </c>
     </row>
     <row r="22">
@@ -1100,13 +1120,13 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.244913673142701</v>
+        <v>0.249254235374948</v>
       </c>
       <c r="D22" t="n">
-        <v>3.2674244746727</v>
+        <v>24.93</v>
       </c>
       <c r="E22" t="n">
-        <v>24.49</v>
+        <v>3.23488709521482</v>
       </c>
     </row>
     <row r="23">
@@ -1117,13 +1137,13 @@
         <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>0.241556384788178</v>
+        <v>0.253429349349366</v>
       </c>
       <c r="D23" t="n">
-        <v>1.55568983384528</v>
+        <v>25.34</v>
       </c>
       <c r="E23" t="n">
-        <v>24.16</v>
+        <v>1.48212624796213</v>
       </c>
     </row>
     <row r="24">
@@ -1134,13 +1154,13 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.13893507565017</v>
+        <v>0.172756264120203</v>
       </c>
       <c r="D24" t="n">
-        <v>16.2242913160414</v>
+        <v>17.28</v>
       </c>
       <c r="E24" t="n">
-        <v>13.89</v>
+        <v>15.4607994636716</v>
       </c>
     </row>
   </sheetData>
@@ -1165,7 +1185,7 @@
         <v>33</v>
       </c>
       <c r="D1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -1182,10 +1202,10 @@
         <v>31</v>
       </c>
       <c r="D2" t="n">
-        <v>2.26864092765106</v>
+        <v>2.25623000075569</v>
       </c>
       <c r="E2" t="n">
-        <v>213705.771933232</v>
+        <v>208566.151363084</v>
       </c>
     </row>
     <row r="3">
@@ -1196,319 +1216,370 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>4.06120153402493</v>
+        <v>5.38441292750874</v>
       </c>
       <c r="E3" t="n">
-        <v>1463430.69537175</v>
+        <v>1233435.52803022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6807482079489</v>
+        <v>1.31801984955663</v>
       </c>
       <c r="E4" t="n">
-        <v>3745.37810794006</v>
+        <v>198994.908037956</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>7.96248900453676</v>
+        <v>1.35575123440927</v>
       </c>
       <c r="E5" t="n">
-        <v>8693.5799836956</v>
+        <v>8436.7368576976</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D6" t="n">
-        <v>4.01123798425685</v>
+        <v>7.81258703681891</v>
       </c>
       <c r="E6" t="n">
-        <v>136125.791770204</v>
+        <v>8600.00859599406</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="D7" t="n">
-        <v>6.85014917582655</v>
+        <v>0.0752496396590436</v>
       </c>
       <c r="E7" t="n">
-        <v>1649.43203417845</v>
+        <v>1906.1196847482</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>5.25376762935413</v>
+        <v>3.98803982999847</v>
       </c>
       <c r="E8" t="n">
-        <v>1179.28089114645</v>
+        <v>137280.410343388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>2.10577811305707</v>
+        <v>2.05501599388022</v>
       </c>
       <c r="E9" t="n">
-        <v>1096.79125120878</v>
+        <v>4027.18165844523</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>4.21262045164963</v>
+        <v>8.51681481550408</v>
       </c>
       <c r="E10" t="n">
-        <v>26.0660434837536</v>
+        <v>710.483364008151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>5.92905752727299</v>
+        <v>2.13890275428367</v>
       </c>
       <c r="E11" t="n">
-        <v>56282.6746473634</v>
+        <v>940.730508061435</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4.03899779835412</v>
+        <v>4.3070090372524</v>
       </c>
       <c r="E12" t="n">
-        <v>276.479934279954</v>
+        <v>31.4334749638212</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>2.85154236856698</v>
+        <v>5.54954574978561</v>
       </c>
       <c r="E13" t="n">
-        <v>249.981486597994</v>
+        <v>55530.4852673625</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D14" t="n">
-        <v>2.60435297119371</v>
+        <v>5.91244538148531</v>
       </c>
       <c r="E14" t="n">
-        <v>1002.62606493129</v>
+        <v>521.658880940343</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" t="s">
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>2.49338008207189</v>
+        <v>14.5859570297162</v>
       </c>
       <c r="E15" t="n">
-        <v>614.318530576056</v>
+        <v>705.868129697753</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>1.82697939334667</v>
+        <v>2.6757566376574</v>
       </c>
       <c r="E16" t="n">
-        <v>9741.16384132806</v>
+        <v>1021.62267886647</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>3.06490315259725</v>
+        <v>0.708060899050319</v>
       </c>
       <c r="E17" t="n">
-        <v>4793.86718554297</v>
+        <v>1062.12555896263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
         <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>2.84453657101213</v>
+        <v>1.89154911330883</v>
       </c>
       <c r="E18" t="n">
-        <v>3838.25573626451</v>
+        <v>8799.23152575949</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>3.2674244746727</v>
+        <v>1.55601404266236</v>
       </c>
       <c r="E19" t="n">
-        <v>1599.7034947874</v>
+        <v>5061.21321793091</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>1.55568983384528</v>
+        <v>3.09913502283175</v>
       </c>
       <c r="E20" t="n">
-        <v>1515.37339858964</v>
+        <v>4501.92785514261</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" t="n">
+        <v>40</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2.52831076732444</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4016.24392719755</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+      <c r="C22" t="n">
+        <v>35</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3.23488709521482</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1637.46763124693</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s">
+        <v>23</v>
+      </c>
+      <c r="C23" t="n">
+        <v>46</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.48212624796213</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1615.14096911446</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
         <v>29</v>
       </c>
-      <c r="B21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" t="n">
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
         <v>28</v>
       </c>
-      <c r="D21" t="n">
-        <v>16.2242913160414</v>
-      </c>
-      <c r="E21" t="n">
-        <v>146.669525368677</v>
+      <c r="D24" t="n">
+        <v>15.4607994636716</v>
+      </c>
+      <c r="E24" t="n">
+        <v>163.934353869879</v>
       </c>
     </row>
   </sheetData>
@@ -1527,459 +1598,521 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
-        <v>31</v>
-      </c>
       <c r="D1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" t="s">
         <v>34</v>
-      </c>
-      <c r="E1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.279365719412144</v>
+      <c r="B2" t="s">
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>2.26864092765106</v>
+        <v>0.274491213557867</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.553826886638229</v>
+        <v>2.25623000075569</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.825178955136324</v>
+      <c r="B3" t="s">
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>4.06120153402493</v>
+        <v>0.770826612703138</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0834518565407574</v>
+        <v>5.38441292750874</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.52732133779276</v>
+      <c r="B4" t="s">
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.656981044371095</v>
+        <v>0.593818056246074</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.277924654805158</v>
+        <v>1.31801984955663</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.532969487397903</v>
+      <c r="B5" t="s">
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>3.6807482079489</v>
+        <v>0.629854617326747</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.27329765370145</v>
+        <v>1.35575123440927</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="n">
-        <v>0.752979061768441</v>
+      <c r="B6" t="s">
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>7.96248900453676</v>
+        <v>0.750960717843188</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.12321710014041</v>
+        <v>7.81258703681891</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.826678417215016</v>
+      <c r="B7" t="s">
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0683963575558215</v>
+        <v>0.816983242312284</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0826634007135609</v>
+        <v>0.0752496396590436</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
-      <c r="B8" t="n">
-        <v>0.520828806653862</v>
+      <c r="B8" t="s">
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.01123798425685</v>
+        <v>0.522936315833308</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.28330500327083</v>
+        <v>3.98803982999847</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="n">
-        <v>0.162131326836121</v>
+      <c r="B9" t="s">
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>6.85014917582655</v>
+        <v>0.315803347718012</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.790133063142851</v>
+        <v>2.05501599388022</v>
       </c>
       <c r="E9" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.268306149334371</v>
+      <c r="B10" t="s">
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>5.25376762935413</v>
+        <v>0.203899198184402</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.571369373577109</v>
+        <v>8.51681481550408</v>
       </c>
       <c r="E10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.158615236724181</v>
+      <c r="B11" t="s">
+        <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>2.10577811305707</v>
+        <v>0.139187456422384</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.799655096290825</v>
+        <v>2.13890275428367</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="n">
-        <v>0.182195878553904</v>
+      <c r="B12" t="s">
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4.21262045164963</v>
+        <v>0.211768099961836</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.739461451410998</v>
+        <v>4.3070090372524</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>16</v>
       </c>
-      <c r="B13" t="n">
-        <v>0.490358290163932</v>
+      <c r="B13" t="s">
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>5.92905752727299</v>
+        <v>0.486996377527185</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.30948647797175</v>
+        <v>5.54954574978561</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
         <v>18</v>
       </c>
-      <c r="B14" t="n">
-        <v>0.0840752991672098</v>
+      <c r="B14" t="s">
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>4.03899779835412</v>
+        <v>0.138127084649609</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.07533157864982</v>
+        <v>5.91244538148531</v>
       </c>
       <c r="E14" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="n">
-        <v>0.193486895277608</v>
+      <c r="B15" t="s">
+        <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>2.85154236856698</v>
+        <v>0.311247431212778</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.713348444088747</v>
+        <v>14.5859570297162</v>
       </c>
       <c r="E15" t="s">
-        <v>38</v>
-      </c>
-      <c r="F15" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16" t="n">
-        <v>0.48142394922171</v>
+      <c r="B16" t="s">
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>2.60435297119371</v>
+        <v>0.486111369628677</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.317472308834312</v>
+        <v>2.6757566376574</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
-      </c>
-      <c r="F16" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
         <v>21</v>
       </c>
-      <c r="B17" t="n">
-        <v>0.352586808781139</v>
+      <c r="B17" t="s">
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>2.49338008207189</v>
+        <v>0.307583822489706</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.452733939854977</v>
+        <v>0.708060899050319</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
         <v>22</v>
       </c>
-      <c r="B18" t="n">
-        <v>0.343081309845054</v>
+      <c r="B18" t="s">
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>1.82697939334667</v>
+        <v>0.320540501707639</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.464602940504748</v>
+        <v>1.89154911330883</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
         <v>24</v>
       </c>
-      <c r="B19" t="n">
-        <v>0.246484884507112</v>
+      <c r="B19" t="s">
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.987770430596723</v>
+        <v>0.124399328837739</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.608209708339822</v>
+        <v>1.55601404266236</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
         <v>25</v>
       </c>
-      <c r="B20" t="n">
-        <v>0.209175973782021</v>
+      <c r="B20" t="s">
+        <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>3.06490315259725</v>
+        <v>0.212817585744397</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.679488200555833</v>
+        <v>3.09913502283175</v>
       </c>
       <c r="E20" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
         <v>26</v>
       </c>
-      <c r="B21" t="n">
-        <v>0.232350403525653</v>
+      <c r="B21" t="s">
+        <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>2.84453657101213</v>
+        <v>0.246482374091248</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.633856568940172</v>
+        <v>2.52831076732444</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
-      </c>
-      <c r="F21" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
         <v>27</v>
       </c>
-      <c r="B22" t="n">
-        <v>0.244913673142701</v>
+      <c r="B22" t="s">
+        <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>3.2674244746727</v>
+        <v>0.249254235374948</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.610986968224968</v>
+        <v>3.23488709521482</v>
       </c>
       <c r="E22" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
         <v>28</v>
       </c>
-      <c r="B23" t="n">
-        <v>0.241556384788178</v>
+      <c r="B23" t="s">
+        <v>23</v>
       </c>
       <c r="C23" t="n">
-        <v>1.55568983384528</v>
+        <v>0.253429349349366</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.616981478808273</v>
+        <v>1.48212624796213</v>
       </c>
       <c r="E23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" t="s">
-        <v>23</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s">
+        <v>23</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.172756264120203</v>
+      </c>
+      <c r="D24" t="n">
+        <v>15.4607994636716</v>
+      </c>
+      <c r="E24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" t="n">
+        <v>25.614460776583</v>
+      </c>
+      <c r="C2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B3" t="n">
+        <v>10.084121007252</v>
+      </c>
+      <c r="C3" t="n">
+        <v>60.6311407637714</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="n">
+        <v>7.58114335638022</v>
+      </c>
+      <c r="C4" t="n">
+        <v>24.8209799254861</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5.13178181007681</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32.3086034805297</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>3.1500828920741</v>
+      </c>
+      <c r="C6" t="n">
+        <v>38.6161959207117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>25.614460776583</v>
+      </c>
+      <c r="C2" t="n">
+        <v>10.084121007252</v>
+      </c>
+      <c r="D2" t="n">
+        <v>60.6311407637714</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -532,7 +532,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8436.7368576976</v>
+        <v>8179.716350703</v>
       </c>
     </row>
     <row r="6">
@@ -642,7 +642,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>705.868129697753</v>
+        <v>1029.49366483948</v>
       </c>
     </row>
     <row r="16">
@@ -831,13 +831,13 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.629854617326747</v>
+        <v>0.622613255785912</v>
       </c>
       <c r="D5" t="n">
-        <v>62.99</v>
+        <v>62.26</v>
       </c>
       <c r="E5" t="n">
-        <v>1.35575123440927</v>
+        <v>1.33911575013123</v>
       </c>
     </row>
     <row r="6">
@@ -1001,13 +1001,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.311247431212778</v>
+        <v>0.348450117558607</v>
       </c>
       <c r="D15" t="n">
-        <v>31.12</v>
+        <v>34.85</v>
       </c>
       <c r="E15" t="n">
-        <v>14.5859570297162</v>
+        <v>7.26279853475374</v>
       </c>
     </row>
     <row r="16">
@@ -1253,10 +1253,10 @@
         <v>68</v>
       </c>
       <c r="D5" t="n">
-        <v>1.35575123440927</v>
+        <v>1.33911575013123</v>
       </c>
       <c r="E5" t="n">
-        <v>8436.7368576976</v>
+        <v>8179.716350703</v>
       </c>
     </row>
     <row r="6">
@@ -1423,10 +1423,10 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5859570297162</v>
+        <v>7.26279853475374</v>
       </c>
       <c r="E15" t="n">
-        <v>705.868129697753</v>
+        <v>1029.49366483948</v>
       </c>
     </row>
     <row r="16">
@@ -1669,10 +1669,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.629854617326747</v>
+        <v>0.622613255785912</v>
       </c>
       <c r="D5" t="n">
-        <v>1.35575123440927</v>
+        <v>1.33911575013123</v>
       </c>
       <c r="E5" t="s">
         <v>36</v>
@@ -1839,10 +1839,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.311247431212778</v>
+        <v>0.348450117558607</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5859570297162</v>
+        <v>7.26279853475374</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -2028,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>25.614460776583</v>
+        <v>26.0237156629112</v>
       </c>
       <c r="C2"/>
     </row>
@@ -2037,10 +2037,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>10.084121007252</v>
+        <v>13.5072213066992</v>
       </c>
       <c r="C3" t="n">
-        <v>60.6311407637714</v>
+        <v>48.0964921317921</v>
       </c>
     </row>
     <row r="4">
@@ -2048,10 +2048,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>7.58114335638022</v>
+        <v>9.35427610220778</v>
       </c>
       <c r="C4" t="n">
-        <v>24.8209799254861</v>
+        <v>30.7461106188558</v>
       </c>
     </row>
     <row r="5">
@@ -2059,10 +2059,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>5.13178181007681</v>
+        <v>6.14740786811341</v>
       </c>
       <c r="C5" t="n">
-        <v>32.3086034805297</v>
+        <v>34.2823773753854</v>
       </c>
     </row>
     <row r="6">
@@ -2070,10 +2070,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3.1500828920741</v>
+        <v>3.90517870455359</v>
       </c>
       <c r="C6" t="n">
-        <v>38.6161959207117</v>
+        <v>36.4743841902903</v>
       </c>
     </row>
   </sheetData>
@@ -2106,13 +2106,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>25.614460776583</v>
+        <v>26.0237156629112</v>
       </c>
       <c r="C2" t="n">
-        <v>10.084121007252</v>
+        <v>13.5072213066992</v>
       </c>
       <c r="D2" t="n">
-        <v>60.6311407637714</v>
+        <v>48.0964921317921</v>
       </c>
     </row>
   </sheetData>

--- a/Outcome/Publish/figure_data/fig5.xlsx
+++ b/Outcome/Publish/figure_data/fig5.xlsx
@@ -521,7 +521,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>198994.908037956</v>
+        <v>198994.910071112</v>
       </c>
     </row>
     <row r="5">
@@ -587,7 +587,7 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>710.483364008151</v>
+        <v>710.483368250585</v>
       </c>
     </row>
     <row r="11">
@@ -598,7 +598,7 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>940.730508061435</v>
+        <v>941.808742228531</v>
       </c>
     </row>
     <row r="12">
@@ -620,7 +620,7 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>55530.4852673625</v>
+        <v>57740.5466290565</v>
       </c>
     </row>
     <row r="14">
@@ -631,7 +631,7 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>521.658880940343</v>
+        <v>249.868633941053</v>
       </c>
     </row>
     <row r="15">
@@ -642,7 +642,7 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>1029.49366483948</v>
+        <v>684.322051325585</v>
       </c>
     </row>
     <row r="16">
@@ -653,7 +653,7 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>1021.62267886647</v>
+        <v>1042.49991372976</v>
       </c>
     </row>
     <row r="17">
@@ -664,7 +664,7 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>1062.12555896263</v>
+        <v>1161.73959105307</v>
       </c>
     </row>
     <row r="18">
@@ -686,7 +686,7 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>5061.21321793091</v>
+        <v>2103.174118453</v>
       </c>
     </row>
     <row r="20">
@@ -708,7 +708,7 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>4016.24392719755</v>
+        <v>3622.00955535986</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,7 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>1637.46763124693</v>
+        <v>1638.11793719671</v>
       </c>
     </row>
     <row r="23">
@@ -741,7 +741,7 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>163.934353869879</v>
+        <v>163.934353869906</v>
       </c>
     </row>
   </sheetData>
@@ -814,13 +814,13 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.593818056246074</v>
+        <v>0.593818058710427</v>
       </c>
       <c r="D4" t="n">
         <v>59.38</v>
       </c>
       <c r="E4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
     </row>
     <row r="5">
@@ -916,13 +916,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.203899198184402</v>
+        <v>0.203899199153672</v>
       </c>
       <c r="D10" t="n">
         <v>20.39</v>
       </c>
       <c r="E10" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
     </row>
     <row r="11">
@@ -933,13 +933,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.139187456422384</v>
+        <v>0.139324761711829</v>
       </c>
       <c r="D11" t="n">
-        <v>13.92</v>
+        <v>13.93</v>
       </c>
       <c r="E11" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
     </row>
     <row r="12">
@@ -967,13 +967,13 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.486996377527185</v>
+        <v>0.49675036211565</v>
       </c>
       <c r="D13" t="n">
-        <v>48.7</v>
+        <v>49.68</v>
       </c>
       <c r="E13" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
     </row>
     <row r="14">
@@ -984,13 +984,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.138127084649609</v>
+        <v>0.0766029113928961</v>
       </c>
       <c r="D14" t="n">
-        <v>13.81</v>
+        <v>7.66</v>
       </c>
       <c r="E14" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
     </row>
     <row r="15">
@@ -1001,13 +1001,13 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.348450117558607</v>
+        <v>0.321531250827086</v>
       </c>
       <c r="D15" t="n">
-        <v>34.85</v>
+        <v>32.15</v>
       </c>
       <c r="E15" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
     </row>
     <row r="16">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.486111369628677</v>
+        <v>0.491166057056667</v>
       </c>
       <c r="D16" t="n">
-        <v>48.61</v>
+        <v>49.12</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
     </row>
     <row r="17">
@@ -1035,13 +1035,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.307583822489706</v>
+        <v>0.326998239324576</v>
       </c>
       <c r="D17" t="n">
-        <v>30.76</v>
+        <v>32.7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.708060899050319</v>
+        <v>0.695767449023808</v>
       </c>
     </row>
     <row r="18">
@@ -1069,13 +1069,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124399328837739</v>
+        <v>0.0665073692658114</v>
       </c>
       <c r="D19" t="n">
-        <v>12.44</v>
+        <v>6.65</v>
       </c>
       <c r="E19" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
     </row>
     <row r="20">
@@ -1103,13 +1103,13 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.246482374091248</v>
+        <v>0.25364195600278</v>
       </c>
       <c r="D21" t="n">
-        <v>24.65</v>
+        <v>25.36</v>
       </c>
       <c r="E21" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
     </row>
     <row r="22">
@@ -1120,13 +1120,13 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.249254235374948</v>
+        <v>0.249328543696683</v>
       </c>
       <c r="D22" t="n">
         <v>24.93</v>
       </c>
       <c r="E22" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
     </row>
     <row r="23">
@@ -1154,13 +1154,13 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.172756264120203</v>
+        <v>0.172756264120226</v>
       </c>
       <c r="D24" t="n">
         <v>17.28</v>
       </c>
       <c r="E24" t="n">
-        <v>15.4607994636716</v>
+        <v>15.4607994636717</v>
       </c>
     </row>
   </sheetData>
@@ -1236,10 +1236,10 @@
         <v>66</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
       <c r="E4" t="n">
-        <v>198994.908037956</v>
+        <v>198994.910071112</v>
       </c>
     </row>
     <row r="5">
@@ -1338,10 +1338,10 @@
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
       <c r="E10" t="n">
-        <v>710.483364008151</v>
+        <v>710.483368250585</v>
       </c>
     </row>
     <row r="11">
@@ -1355,10 +1355,10 @@
         <v>24</v>
       </c>
       <c r="D11" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
       <c r="E11" t="n">
-        <v>940.730508061435</v>
+        <v>941.808742228531</v>
       </c>
     </row>
     <row r="12">
@@ -1389,10 +1389,10 @@
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
       <c r="E13" t="n">
-        <v>55530.4852673625</v>
+        <v>57740.5466290565</v>
       </c>
     </row>
     <row r="14">
@@ -1403,13 +1403,13 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
       <c r="E14" t="n">
-        <v>521.658880940343</v>
+        <v>249.868633941053</v>
       </c>
     </row>
     <row r="15">
@@ -1423,10 +1423,10 @@
         <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
       <c r="E15" t="n">
-        <v>1029.49366483948</v>
+        <v>684.322051325585</v>
       </c>
     </row>
     <row r="16">
@@ -1440,10 +1440,10 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
       <c r="E16" t="n">
-        <v>1021.62267886647</v>
+        <v>1042.49991372976</v>
       </c>
     </row>
     <row r="17">
@@ -1457,10 +1457,10 @@
         <v>47</v>
       </c>
       <c r="D17" t="n">
-        <v>0.708060899050319</v>
+        <v>0.695767449023808</v>
       </c>
       <c r="E17" t="n">
-        <v>1062.12555896263</v>
+        <v>1161.73959105307</v>
       </c>
     </row>
     <row r="18">
@@ -1488,13 +1488,13 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
       <c r="E19" t="n">
-        <v>5061.21321793091</v>
+        <v>2103.174118453</v>
       </c>
     </row>
     <row r="20">
@@ -1522,13 +1522,13 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
       <c r="E21" t="n">
-        <v>4016.24392719755</v>
+        <v>3622.00955535986</v>
       </c>
     </row>
     <row r="22">
@@ -1542,10 +1542,10 @@
         <v>35</v>
       </c>
       <c r="D22" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
       <c r="E22" t="n">
-        <v>1637.46763124693</v>
+        <v>1638.11793719671</v>
       </c>
     </row>
     <row r="23">
@@ -1576,10 +1576,10 @@
         <v>28</v>
       </c>
       <c r="D24" t="n">
-        <v>15.4607994636716</v>
+        <v>15.4607994636717</v>
       </c>
       <c r="E24" t="n">
-        <v>163.934353869879</v>
+        <v>163.934353869906</v>
       </c>
     </row>
   </sheetData>
@@ -1652,10 +1652,10 @@
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>0.593818056246074</v>
+        <v>0.593818058710427</v>
       </c>
       <c r="D4" t="n">
-        <v>1.31801984955663</v>
+        <v>1.31801985854874</v>
       </c>
       <c r="E4" t="s">
         <v>36</v>
@@ -1754,13 +1754,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>0.203899198184402</v>
+        <v>0.203899199153672</v>
       </c>
       <c r="D10" t="n">
-        <v>8.51681481550408</v>
+        <v>8.51681486409554</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -1771,10 +1771,10 @@
         <v>11</v>
       </c>
       <c r="C11" t="n">
-        <v>0.139187456422384</v>
+        <v>0.139324761711829</v>
       </c>
       <c r="D11" t="n">
-        <v>2.13890275428367</v>
+        <v>2.13851126674038</v>
       </c>
       <c r="E11" t="s">
         <v>35</v>
@@ -1805,10 +1805,10 @@
         <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>0.486996377527185</v>
+        <v>0.49675036211565</v>
       </c>
       <c r="D13" t="n">
-        <v>5.54954574978561</v>
+        <v>5.27889248759791</v>
       </c>
       <c r="E13" t="s">
         <v>36</v>
@@ -1822,10 +1822,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>0.138127084649609</v>
+        <v>0.0766029113928961</v>
       </c>
       <c r="D14" t="n">
-        <v>5.91244538148531</v>
+        <v>4.34103148571146</v>
       </c>
       <c r="E14" t="s">
         <v>35</v>
@@ -1839,10 +1839,10 @@
         <v>17</v>
       </c>
       <c r="C15" t="n">
-        <v>0.348450117558607</v>
+        <v>0.321531250827086</v>
       </c>
       <c r="D15" t="n">
-        <v>7.26279853475374</v>
+        <v>17.8885309688549</v>
       </c>
       <c r="E15" t="s">
         <v>37</v>
@@ -1856,10 +1856,10 @@
         <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>0.486111369628677</v>
+        <v>0.491166057056667</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6757566376574</v>
+        <v>2.66345767681024</v>
       </c>
       <c r="E16" t="s">
         <v>36</v>
@@ -1873,10 +1873,10 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>0.307583822489706</v>
+        <v>0.326998239324576</v>
       </c>
       <c r="D17" t="n">
-        <v>0.708060899050319</v>
+        <v>0.695767449023808</v>
       </c>
       <c r="E17" t="s">
         <v>35</v>
@@ -1907,10 +1907,10 @@
         <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>0.124399328837739</v>
+        <v>0.0665073692658114</v>
       </c>
       <c r="D19" t="n">
-        <v>1.55601404266236</v>
+        <v>1.92277733046749</v>
       </c>
       <c r="E19" t="s">
         <v>35</v>
@@ -1941,10 +1941,10 @@
         <v>23</v>
       </c>
       <c r="C21" t="n">
-        <v>0.246482374091248</v>
+        <v>0.25364195600278</v>
       </c>
       <c r="D21" t="n">
-        <v>2.52831076732444</v>
+        <v>2.70630202222186</v>
       </c>
       <c r="E21" t="s">
         <v>35</v>
@@ -1958,10 +1958,10 @@
         <v>23</v>
       </c>
       <c r="C22" t="n">
-        <v>0.249254235374948</v>
+        <v>0.249328543696683</v>
       </c>
       <c r="D22" t="n">
-        <v>3.23488709521482</v>
+        <v>3.23441633610315</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
@@ -1992,10 +1992,10 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.172756264120203</v>
+        <v>0.172756264120226</v>
       </c>
       <c r="D24" t="n">
-        <v>15.4607994636716</v>
+        <v>15.4607994636717</v>
       </c>
       <c r="E24" t="s">
         <v>37</v>
@@ -2028,7 +2028,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>26.0237156629112</v>
+        <v>25.9906374941884</v>
       </c>
       <c r="C2"/>
     </row>
@@ -2037,10 +2037,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>13.5072213066992</v>
+        <v>9.36412556644216</v>
       </c>
       <c r="C3" t="n">
-        <v>48.0964921317921</v>
+        <v>63.9711585814853</v>
       </c>
     </row>
     <row r="4">
@@ -2048,10 +2048,10 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>9.35427610220778</v>
+        <v>7.05623482198502</v>
       </c>
       <c r="C4" t="n">
-        <v>30.7461106188558</v>
+        <v>24.6460892486089</v>
       </c>
     </row>
     <row r="5">
@@ -2059,10 +2059,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>6.14740786811341</v>
+        <v>5.22288168209788</v>
       </c>
       <c r="C5" t="n">
-        <v>34.2823773753854</v>
+        <v>25.982031297697</v>
       </c>
     </row>
     <row r="6">
@@ -2070,10 +2070,10 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>3.90517870455359</v>
+        <v>3.68044312846169</v>
       </c>
       <c r="C6" t="n">
-        <v>36.4743841902903</v>
+        <v>29.5323280809347</v>
       </c>
     </row>
   </sheetData>
@@ -2106,13 +2106,13 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>26.0237156629112</v>
+        <v>25.9906374941884</v>
       </c>
       <c r="C2" t="n">
-        <v>13.5072213066992</v>
+        <v>9.36412556644216</v>
       </c>
       <c r="D2" t="n">
-        <v>48.0964921317921</v>
+        <v>63.9711585814853</v>
       </c>
     </row>
   </sheetData>
